--- a/results/PRISM/prism_candidate_bootstrap_stability.xlsx
+++ b/results/PRISM/prism_candidate_bootstrap_stability.xlsx
@@ -14,11 +14,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>DRUG</t>
   </si>
   <si>
+    <t>BRD_ID</t>
+  </si>
+  <si>
     <t>N_CELL_LINES</t>
   </si>
   <si>
@@ -40,13 +43,22 @@
     <t>N_BOOTSTRAP_VALID</t>
   </si>
   <si>
-    <t>ALVESPIMYCIN (BRD:BRD-K83988098-001-02-0)</t>
-  </si>
-  <si>
-    <t>DOCETAXEL (BRD:BRD-K30577245-001-05-0)</t>
-  </si>
-  <si>
-    <t>PACLITAXEL (BRD:BRD-K62008436-001-23-9)</t>
+    <t>ALVESPIMYCIN</t>
+  </si>
+  <si>
+    <t>DOCETAXEL</t>
+  </si>
+  <si>
+    <t>PACLITAXEL</t>
+  </si>
+  <si>
+    <t>BRD-K83988098-001-02-0</t>
+  </si>
+  <si>
+    <t>BRD-K30577245-001-05-0</t>
+  </si>
+  <si>
+    <t>BRD-K62008436-001-23-9</t>
   </si>
 </sst>
 </file>
@@ -378,10 +390,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -406,82 +418,94 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2">
         <v>43</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>-0.6055572334642102</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>-0.6085474221446279</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>-0.8055512034514078</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>-0.3403957148407495</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>1</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3">
         <v>43</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>-0.5756569012382966</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>-0.5703367454105033</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>-0.7412976984597928</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>-0.3220807001745613</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>1</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4">
         <v>43</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>-0.5514950166112957</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>-0.556692499786307</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>-0.7472160808163039</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>-0.2956038134996279</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>1</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>1000</v>
       </c>
     </row>
